--- a/media/Levels/Level_10.xlsx
+++ b/media/Levels/Level_10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A488F924-3315-4084-B93A-85508C66D695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0294647B-CFC4-4740-B90C-44E02179FC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A0C67C02-248C-4072-B780-40C676E51687}"/>
   </bookViews>
@@ -2036,7 +2036,7 @@
     </row>
     <row r="8" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="11" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" s="1">
         <v>0</v>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="14" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="1">
         <v>0</v>
@@ -2999,7 +2999,7 @@
     </row>
     <row r="17" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P17" s="1">
         <v>0</v>
@@ -3239,7 +3239,7 @@
     </row>
     <row r="20" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S20" s="1">
         <v>0</v>
@@ -3455,7 +3455,7 @@
     </row>
     <row r="23" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
@@ -3599,7 +3599,7 @@
     </row>
     <row r="26" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" s="4">
         <v>0</v>
@@ -3743,7 +3743,7 @@
     </row>
     <row r="29" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB29" s="1">
         <v>0</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="32" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE32" s="1">
         <v>0</v>
@@ -4037,7 +4037,7 @@
     </row>
     <row r="35" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH35" s="1">
         <v>0</v>
@@ -4130,7 +4130,7 @@
     </row>
     <row r="38" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S38" s="4">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     </row>
     <row r="41" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S41" s="4">
         <v>0</v>
@@ -4478,7 +4478,7 @@
     </row>
     <row r="44" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44" s="2">
         <v>0</v>
@@ -4766,7 +4766,7 @@
     </row>
     <row r="47" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A47" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
@@ -5045,7 +5045,7 @@
     </row>
     <row r="50" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A50" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H50" s="2">
         <v>0</v>
@@ -5321,7 +5321,7 @@
     </row>
     <row r="53" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A53" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H53" s="2">
         <v>0</v>
@@ -5588,7 +5588,7 @@
     </row>
     <row r="56" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A56" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2">
         <v>0</v>
@@ -5864,7 +5864,7 @@
     </row>
     <row r="59" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A59" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="62" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A62" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS62" s="3">
         <v>0</v>
@@ -6257,7 +6257,7 @@
     </row>
     <row r="65" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A65" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BO65" s="2">
         <v>0</v>
@@ -6527,7 +6527,7 @@
     </row>
     <row r="68" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A68" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL68" s="1">
         <v>0</v>
@@ -6806,7 +6806,7 @@
     </row>
     <row r="71" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A71" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT71" s="1">
         <v>0</v>
@@ -7064,7 +7064,7 @@
     </row>
     <row r="74" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A74" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT74" s="1">
         <v>0</v>
@@ -7532,7 +7532,7 @@
     </row>
     <row r="77" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A77" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT77" s="1">
         <v>0</v>
@@ -7763,7 +7763,7 @@
     </row>
     <row r="80" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A80" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT80" s="1">
         <v>0</v>
@@ -7997,7 +7997,7 @@
     </row>
     <row r="83" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A83" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT83" s="1">
         <v>0</v>
@@ -8225,7 +8225,7 @@
     </row>
     <row r="86" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A86" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T86" s="3">
         <v>0</v>
@@ -8450,7 +8450,7 @@
     </row>
     <row r="89" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A89" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q89" s="3">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     </row>
     <row r="92" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A92" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I92" s="4">
         <v>0</v>
@@ -8690,7 +8690,7 @@
     </row>
     <row r="95" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A95" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I95" s="4">
         <v>0</v>
@@ -8780,7 +8780,7 @@
     </row>
     <row r="98" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A98" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J98" s="5">
         <v>0</v>
@@ -8927,7 +8927,7 @@
     </row>
     <row r="101" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A101" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J101" s="3">
         <v>0</v>
@@ -9155,7 +9155,7 @@
     </row>
     <row r="104" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A104" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J104" s="3">
         <v>0</v>
@@ -9275,7 +9275,7 @@
     </row>
     <row r="107" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A107" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J107" s="3">
         <v>0</v>
@@ -9365,7 +9365,7 @@
     </row>
     <row r="110" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A110" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J110" s="3">
         <v>0</v>
@@ -9461,7 +9461,7 @@
     </row>
     <row r="113" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A113" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K113" s="3">
         <v>0</v>
@@ -9557,7 +9557,7 @@
     </row>
     <row r="116" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A116" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N116" s="3">
         <v>0</v>
@@ -9707,7 +9707,7 @@
     </row>
     <row r="119" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A119" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P119" s="4">
         <v>0</v>
@@ -9911,7 +9911,7 @@
     </row>
     <row r="122" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A122" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P122" s="4">
         <v>0</v>
@@ -10142,7 +10142,7 @@
     </row>
     <row r="125" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A125" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P125" s="2">
         <v>0</v>
@@ -10571,7 +10571,7 @@
     </row>
     <row r="128" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A128" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P128" s="2">
         <v>0</v>
@@ -10994,7 +10994,7 @@
     </row>
     <row r="131" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A131" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P131" s="2">
         <v>0</v>
@@ -11411,7 +11411,7 @@
     </row>
     <row r="134" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A134" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P134" s="2">
         <v>0</v>
@@ -11843,7 +11843,7 @@
     </row>
     <row r="137" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A137" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O137" s="1">
         <v>3</v>
@@ -12329,7 +12329,7 @@
     </row>
     <row r="140" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A140" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L140" s="1">
         <v>3</v>
@@ -12785,7 +12785,7 @@
     </row>
     <row r="143" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A143" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I143" s="1">
         <v>3</v>

--- a/media/Levels/Level_10.xlsx
+++ b/media/Levels/Level_10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0294647B-CFC4-4740-B90C-44E02179FC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059AA8BF-8EB6-4392-AEBA-B6CC203AF281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A0C67C02-248C-4072-B780-40C676E51687}"/>
   </bookViews>
@@ -7333,7 +7333,7 @@
         <v>0</v>
       </c>
       <c r="DC75" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="DD75" s="1">
         <v>0</v>
@@ -8496,9 +8496,6 @@
       <c r="DE90" s="1">
         <v>4</v>
       </c>
-      <c r="DN90" s="1">
-        <v>0</v>
-      </c>
       <c r="EP90" s="1">
         <v>0</v>
       </c>
@@ -8540,8 +8537,8 @@
       <c r="DF91" s="1">
         <v>0</v>
       </c>
-      <c r="DN91" s="1">
-        <v>2</v>
+      <c r="DQ91" s="1">
+        <v>0</v>
       </c>
       <c r="EP91" s="1">
         <v>2</v>
@@ -8587,8 +8584,8 @@
       <c r="DG92" s="1">
         <v>0</v>
       </c>
-      <c r="DN92" s="1">
-        <v>0</v>
+      <c r="DQ92" s="1">
+        <v>2</v>
       </c>
       <c r="EP92" s="1">
         <v>0</v>
@@ -8628,7 +8625,7 @@
       <c r="DH93" s="1">
         <v>4</v>
       </c>
-      <c r="DN93" s="1">
+      <c r="DQ93" s="1">
         <v>0</v>
       </c>
       <c r="EP93" s="1">
@@ -8678,8 +8675,8 @@
       <c r="DI94" s="1">
         <v>0</v>
       </c>
-      <c r="DN94" s="1">
-        <v>2</v>
+      <c r="DQ94" s="1">
+        <v>0</v>
       </c>
       <c r="EP94" s="1">
         <v>2</v>
@@ -8716,8 +8713,8 @@
       <c r="BW95" s="1">
         <v>0</v>
       </c>
-      <c r="DN95" s="1">
-        <v>0</v>
+      <c r="DQ95" s="1">
+        <v>2</v>
       </c>
       <c r="EP95" s="1">
         <v>0</v>
@@ -8742,7 +8739,7 @@
       <c r="BX96" s="1">
         <v>4</v>
       </c>
-      <c r="DN96" s="1">
+      <c r="DQ96" s="1">
         <v>0</v>
       </c>
       <c r="EP96" s="1">
@@ -8768,8 +8765,8 @@
       <c r="BY97" s="1">
         <v>0</v>
       </c>
-      <c r="DN97" s="1">
-        <v>2</v>
+      <c r="DQ97" s="1">
+        <v>0</v>
       </c>
       <c r="EP97" s="1">
         <v>2</v>
@@ -8821,8 +8818,8 @@
       <c r="DD98" s="1">
         <v>0</v>
       </c>
-      <c r="DN98" s="1">
-        <v>0</v>
+      <c r="DQ98" s="1">
+        <v>2</v>
       </c>
       <c r="EP98" s="1">
         <v>0</v>
@@ -8853,7 +8850,10 @@
       <c r="DE99" s="1">
         <v>0</v>
       </c>
-      <c r="DN99" s="1">
+      <c r="DP99" s="1">
+        <v>0</v>
+      </c>
+      <c r="DQ99" s="1">
         <v>0</v>
       </c>
       <c r="DT99" s="4">
@@ -8900,8 +8900,11 @@
       <c r="DF100" s="1">
         <v>4</v>
       </c>
-      <c r="DN100" s="1">
-        <v>2</v>
+      <c r="DO100" s="1">
+        <v>3</v>
+      </c>
+      <c r="DQ100" s="1">
+        <v>0</v>
       </c>
       <c r="DT100" s="4">
         <v>0</v>
@@ -9001,11 +9004,11 @@
       <c r="DG101" s="1">
         <v>0</v>
       </c>
-      <c r="DM101" s="1">
-        <v>0</v>
-      </c>
       <c r="DN101" s="1">
         <v>0</v>
+      </c>
+      <c r="DQ101" s="1">
+        <v>2</v>
       </c>
       <c r="DT101" s="4">
         <v>0</v>
@@ -9063,10 +9066,10 @@
       <c r="DH102" s="1">
         <v>0</v>
       </c>
-      <c r="DL102" s="1">
-        <v>3</v>
-      </c>
-      <c r="DN102" s="1">
+      <c r="DM102" s="1">
+        <v>0</v>
+      </c>
+      <c r="DQ102" s="1">
         <v>0</v>
       </c>
       <c r="DT102" s="4">
@@ -9125,11 +9128,11 @@
       <c r="DI103" s="1">
         <v>4</v>
       </c>
-      <c r="DK103" s="1">
-        <v>0</v>
-      </c>
-      <c r="DN103" s="1">
-        <v>2</v>
+      <c r="DL103" s="1">
+        <v>3</v>
+      </c>
+      <c r="DQ103" s="1">
+        <v>0</v>
       </c>
       <c r="DT103" s="4">
         <v>0</v>
@@ -9190,8 +9193,11 @@
       <c r="DJ104" s="1">
         <v>0</v>
       </c>
-      <c r="DN104" s="1">
-        <v>0</v>
+      <c r="DK104" s="1">
+        <v>0</v>
+      </c>
+      <c r="DQ104" s="1">
+        <v>2</v>
       </c>
       <c r="EJ104" s="1">
         <v>0</v>
@@ -9232,6 +9238,9 @@
         <v>0</v>
       </c>
       <c r="DA105" s="1">
+        <v>0</v>
+      </c>
+      <c r="DQ105" s="1">
         <v>0</v>
       </c>
       <c r="EI105" s="1">

--- a/media/Levels/Level_10.xlsx
+++ b/media/Levels/Level_10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059AA8BF-8EB6-4392-AEBA-B6CC203AF281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52070422-8ED8-4F63-9630-67B0E1310496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A0C67C02-248C-4072-B780-40C676E51687}"/>
   </bookViews>
@@ -182,7 +182,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -389,12 +389,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -643,7 +637,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -660,9 +654,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5478,7 +5469,7 @@
       <c r="AT54" s="1">
         <v>2</v>
       </c>
-      <c r="BS54" s="1">
+      <c r="BS54" s="3">
         <v>0</v>
       </c>
       <c r="BX54" s="4">
@@ -5497,9 +5488,6 @@
         <v>0</v>
       </c>
       <c r="DB54" s="1">
-        <v>0</v>
-      </c>
-      <c r="EP54" s="1">
         <v>0</v>
       </c>
       <c r="ET54" s="1">
@@ -5573,15 +5561,12 @@
       <c r="AT55" s="1">
         <v>0</v>
       </c>
-      <c r="BS55" s="1">
-        <v>2</v>
+      <c r="BS55" s="3">
+        <v>6</v>
       </c>
       <c r="DB55" s="1">
         <v>2</v>
       </c>
-      <c r="EO55" s="1">
-        <v>3</v>
-      </c>
       <c r="ET55" s="1">
         <v>0</v>
       </c>
@@ -5665,13 +5650,10 @@
       <c r="BF56" s="4">
         <v>0</v>
       </c>
-      <c r="BS56" s="1">
+      <c r="BS56" s="3">
         <v>0</v>
       </c>
       <c r="DB56" s="1">
-        <v>0</v>
-      </c>
-      <c r="EN56" s="1">
         <v>0</v>
       </c>
       <c r="ET56" s="1">
@@ -5757,7 +5739,7 @@
       <c r="BF57" s="4">
         <v>0</v>
       </c>
-      <c r="BS57" s="1">
+      <c r="BS57" s="3">
         <v>0</v>
       </c>
       <c r="DB57" s="1">
@@ -5849,8 +5831,8 @@
       <c r="BF58" s="4">
         <v>0</v>
       </c>
-      <c r="BS58" s="1">
-        <v>2</v>
+      <c r="BS58" s="3">
+        <v>6</v>
       </c>
       <c r="DB58" s="1">
         <v>2</v>
@@ -5941,7 +5923,7 @@
       <c r="BF59" s="4">
         <v>0</v>
       </c>
-      <c r="BS59" s="1">
+      <c r="BS59" s="3">
         <v>0</v>
       </c>
       <c r="DB59" s="1">
@@ -6048,7 +6030,7 @@
       <c r="BF60" s="4">
         <v>0</v>
       </c>
-      <c r="BS60" s="3">
+      <c r="BS60" s="1">
         <v>0</v>
       </c>
       <c r="DB60" s="1">
@@ -6140,8 +6122,8 @@
       <c r="AA61" s="2">
         <v>0</v>
       </c>
-      <c r="BS61" s="3">
-        <v>6</v>
+      <c r="BS61" s="1">
+        <v>2</v>
       </c>
       <c r="DB61" s="1">
         <v>2</v>
@@ -6172,7 +6154,7 @@
       <c r="A62" s="1">
         <v>0</v>
       </c>
-      <c r="BS62" s="3">
+      <c r="BS62" s="1">
         <v>0</v>
       </c>
       <c r="DB62" s="1">
@@ -6204,7 +6186,7 @@
       <c r="A63" s="1">
         <v>0</v>
       </c>
-      <c r="BS63" s="3">
+      <c r="BS63" s="1">
         <v>0</v>
       </c>
       <c r="DB63" s="1">
@@ -6239,8 +6221,8 @@
       <c r="A64" s="1">
         <v>0</v>
       </c>
-      <c r="BS64" s="3">
-        <v>6</v>
+      <c r="BS64" s="1">
+        <v>2</v>
       </c>
       <c r="DB64" s="1">
         <v>2</v>
@@ -6271,38 +6253,38 @@
       <c r="BR65" s="2">
         <v>0</v>
       </c>
-      <c r="BS65" s="6">
-        <v>0</v>
-      </c>
-      <c r="BT65" s="6">
-        <v>0</v>
-      </c>
-      <c r="BU65" s="6">
-        <v>0</v>
-      </c>
-      <c r="BV65" s="6">
-        <v>0</v>
-      </c>
-      <c r="BW65" s="6">
-        <v>0</v>
-      </c>
-      <c r="BX65" s="6">
-        <v>12</v>
-      </c>
-      <c r="BY65" s="6">
-        <v>0</v>
-      </c>
-      <c r="BZ65" s="6">
-        <v>0</v>
-      </c>
-      <c r="CA65" s="6">
-        <v>0</v>
-      </c>
-      <c r="CB65" s="6">
-        <v>0</v>
-      </c>
-      <c r="CC65" s="6">
-        <v>12</v>
+      <c r="BS65" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT65" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU65" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV65" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW65" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX65" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY65" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ65" s="2">
+        <v>0</v>
+      </c>
+      <c r="CA65" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB65" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC65" s="2">
+        <v>0</v>
       </c>
       <c r="CD65" s="2">
         <v>0</v>
@@ -8112,38 +8094,38 @@
       <c r="BR84" s="2">
         <v>0</v>
       </c>
-      <c r="BS84" s="6">
-        <v>0</v>
-      </c>
-      <c r="BT84" s="6">
-        <v>0</v>
-      </c>
-      <c r="BU84" s="6">
-        <v>0</v>
-      </c>
-      <c r="BV84" s="6">
-        <v>0</v>
-      </c>
-      <c r="BW84" s="6">
-        <v>0</v>
-      </c>
-      <c r="BX84" s="6">
-        <v>12</v>
-      </c>
-      <c r="BY84" s="6">
-        <v>0</v>
-      </c>
-      <c r="BZ84" s="6">
-        <v>0</v>
-      </c>
-      <c r="CA84" s="6">
-        <v>0</v>
-      </c>
-      <c r="CB84" s="6">
-        <v>0</v>
-      </c>
-      <c r="CC84" s="6">
-        <v>12</v>
+      <c r="BS84" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT84" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU84" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV84" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW84" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX84" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY84" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ84" s="2">
+        <v>0</v>
+      </c>
+      <c r="CA84" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB84" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC84" s="2">
+        <v>0</v>
       </c>
       <c r="CD84" s="2">
         <v>0</v>
@@ -8201,8 +8183,8 @@
       <c r="AT85" s="1">
         <v>2</v>
       </c>
-      <c r="BS85" s="3">
-        <v>6</v>
+      <c r="BS85" s="1">
+        <v>2</v>
       </c>
       <c r="CT85" s="1">
         <v>3</v>
@@ -8287,7 +8269,7 @@
       <c r="AT86" s="1">
         <v>0</v>
       </c>
-      <c r="BS86" s="3">
+      <c r="BS86" s="1">
         <v>0</v>
       </c>
       <c r="CS86" s="1">

--- a/media/Levels/Level_10.xlsx
+++ b/media/Levels/Level_10.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52070422-8ED8-4F63-9630-67B0E1310496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD7F37D1-96BD-4B95-80F4-874F25E98741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A0C67C02-248C-4072-B780-40C676E51687}"/>
   </bookViews>
   <sheets>
-    <sheet name="Level_3" sheetId="1" r:id="rId1"/>
+    <sheet name="Level_10" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -3212,8 +3212,8 @@
       <c r="DN19" s="2">
         <v>0</v>
       </c>
-      <c r="DO19" s="2">
-        <v>0</v>
+      <c r="DO19" s="3">
+        <v>8</v>
       </c>
       <c r="DP19" s="2">
         <v>0</v>
@@ -3301,7 +3301,7 @@
       <c r="DO20" s="2">
         <v>0</v>
       </c>
-      <c r="DP20" s="2">
+      <c r="DP20" s="3">
         <v>0</v>
       </c>
       <c r="DQ20" s="2">
@@ -3390,7 +3390,7 @@
       <c r="DP21" s="2">
         <v>0</v>
       </c>
-      <c r="DQ21" s="2">
+      <c r="DQ21" s="3">
         <v>0</v>
       </c>
       <c r="EB21" s="1">

--- a/media/Levels/Level_10.xlsx
+++ b/media/Levels/Level_10.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\2024年３月特別授業\BaseCross64\DoctorRemote\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD7F37D1-96BD-4B95-80F4-874F25E98741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA5C2FF-03B0-4496-9A39-D65ADF5A5F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A0C67C02-248C-4072-B780-40C676E51687}"/>
   </bookViews>
@@ -1263,10 +1263,10 @@
         <v>0</v>
       </c>
       <c r="BW1" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BX1" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BY1" s="1">
         <v>0</v>
@@ -13303,10 +13303,10 @@
         <v>0</v>
       </c>
       <c r="BW150" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BX150" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BY150" s="1">
         <v>0</v>
